--- a/excel/Glass.xlsx
+++ b/excel/Glass.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ritar/Desktop/SP684-SupplierInfo/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{5B2E9634-28BD-4341-881E-473E8CFA57E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{0E6F1CBA-5FD2-594A-B99B-3F2BFD18ABBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="18000" tabRatio="721" xr2:uid="{769D5609-44B8-DF40-A386-87CBF6C45798}"/>
+    <workbookView xWindow="-20" yWindow="600" windowWidth="28800" windowHeight="15860" tabRatio="721" xr2:uid="{769D5609-44B8-DF40-A386-87CBF6C45798}"/>
   </bookViews>
   <sheets>
     <sheet name="float" sheetId="1" r:id="rId1"/>
@@ -4772,12 +4772,36 @@
     <xf numFmtId="164" fontId="10" fillId="0" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="21" fillId="5" borderId="129" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="5" borderId="130" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="21" fillId="5" borderId="125" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="21" fillId="5" borderId="126" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="123" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="124" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="80" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="66" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="131" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="78" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="5" borderId="74" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4789,30 +4813,6 @@
     </xf>
     <xf numFmtId="164" fontId="21" fillId="5" borderId="128" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="5" borderId="129" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="5" borderId="130" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="123" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="124" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="80" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="66" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="131" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="78" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -5187,7 +5187,7 @@
     <col min="1" max="1" width="1.796875" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.796875" style="2" customWidth="1"/>
     <col min="3" max="3" width="14" style="1" customWidth="1"/>
-    <col min="4" max="4" width="3.796875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="6.3984375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15" style="9" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="1.19921875" style="9" customWidth="1"/>
     <col min="7" max="11" width="8.796875" style="4" customWidth="1"/>
@@ -5535,10 +5535,10 @@
       <c r="C6" s="160" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="163"/>
-      <c r="E6" s="161" t="s">
+      <c r="D6" s="161" t="s">
         <v>0</v>
       </c>
+      <c r="E6" s="161"/>
       <c r="F6" s="162"/>
       <c r="G6" s="92" t="s">
         <v>52</v>
@@ -5880,12 +5880,24 @@
         <v>23</v>
       </c>
       <c r="F9" s="271"/>
-      <c r="G9" s="260"/>
-      <c r="H9" s="273"/>
-      <c r="I9" s="273"/>
-      <c r="J9" s="273"/>
-      <c r="K9" s="273"/>
-      <c r="L9" s="270"/>
+      <c r="G9" s="260">
+        <v>10</v>
+      </c>
+      <c r="H9" s="273">
+        <v>8</v>
+      </c>
+      <c r="I9" s="273">
+        <v>12</v>
+      </c>
+      <c r="J9" s="273">
+        <v>15</v>
+      </c>
+      <c r="K9" s="273">
+        <v>20</v>
+      </c>
+      <c r="L9" s="270">
+        <v>22</v>
+      </c>
       <c r="M9" s="3"/>
       <c r="N9" s="241"/>
       <c r="O9" s="273"/>
@@ -33631,15 +33643,15 @@
     <col min="4" max="4" width="3.796875" style="1" customWidth="1"/>
     <col min="5" max="5" width="4.19921875" style="9" customWidth="1"/>
     <col min="6" max="6" width="1.19921875" style="9" customWidth="1"/>
-    <col min="7" max="9" width="8.3984375" style="4" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="8.3984375" style="13" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="1" style="13" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="9.19921875" style="4" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="8.796875" style="4" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="9.19921875" style="4" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="8.3984375" style="13" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="1.3984375" style="13" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="6.19921875" style="335" hidden="1" customWidth="1"/>
+    <col min="7" max="9" width="8.3984375" style="4" customWidth="1"/>
+    <col min="10" max="10" width="8.3984375" style="13" customWidth="1"/>
+    <col min="11" max="11" width="1" style="13" customWidth="1"/>
+    <col min="12" max="12" width="9.19921875" style="4" customWidth="1"/>
+    <col min="13" max="13" width="8.796875" style="4" customWidth="1"/>
+    <col min="14" max="14" width="9.19921875" style="4" customWidth="1"/>
+    <col min="15" max="15" width="8.3984375" style="13" customWidth="1"/>
+    <col min="16" max="16" width="1.3984375" style="13" customWidth="1"/>
+    <col min="17" max="17" width="6.19921875" style="335" customWidth="1"/>
     <col min="18" max="18" width="7.796875" style="325" customWidth="1"/>
     <col min="19" max="19" width="7.796875" style="4" customWidth="1"/>
     <col min="20" max="21" width="7.796875" style="11" customWidth="1"/>
@@ -33957,10 +33969,18 @@
       </c>
       <c r="E7" s="281"/>
       <c r="F7" s="282"/>
-      <c r="G7" s="348"/>
-      <c r="H7" s="349"/>
-      <c r="I7" s="349"/>
-      <c r="J7" s="350"/>
+      <c r="G7" s="348">
+        <v>10</v>
+      </c>
+      <c r="H7" s="349">
+        <v>20</v>
+      </c>
+      <c r="I7" s="349">
+        <v>18</v>
+      </c>
+      <c r="J7" s="350">
+        <v>15</v>
+      </c>
       <c r="K7" s="3"/>
       <c r="L7" s="348"/>
       <c r="M7" s="349"/>
@@ -34770,10 +34790,18 @@
       </c>
       <c r="E18" s="258"/>
       <c r="F18" s="259"/>
-      <c r="G18" s="362"/>
-      <c r="H18" s="273"/>
-      <c r="I18" s="273"/>
-      <c r="J18" s="270"/>
+      <c r="G18" s="362">
+        <v>10</v>
+      </c>
+      <c r="H18" s="273">
+        <v>20</v>
+      </c>
+      <c r="I18" s="273">
+        <v>15</v>
+      </c>
+      <c r="J18" s="270">
+        <v>10</v>
+      </c>
       <c r="K18" s="3"/>
       <c r="L18" s="241"/>
       <c r="M18" s="273"/>
@@ -39180,15 +39208,15 @@
       </c>
     </row>
     <row r="6" spans="2:14" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="577" t="s">
+      <c r="B6" s="579" t="s">
         <v>82</v>
       </c>
-      <c r="C6" s="578"/>
+      <c r="C6" s="580"/>
       <c r="D6" s="114"/>
-      <c r="E6" s="579" t="s">
+      <c r="E6" s="587" t="s">
         <v>82</v>
       </c>
-      <c r="F6" s="580"/>
+      <c r="F6" s="588"/>
       <c r="G6" s="242" t="s">
         <v>52</v>
       </c>
@@ -40334,15 +40362,15 @@
       </c>
     </row>
     <row r="49" spans="2:13" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="577" t="s">
+      <c r="B49" s="579" t="s">
         <v>85</v>
       </c>
-      <c r="C49" s="578"/>
+      <c r="C49" s="580"/>
       <c r="D49" s="138"/>
-      <c r="E49" s="579" t="s">
+      <c r="E49" s="587" t="s">
         <v>82</v>
       </c>
-      <c r="F49" s="580"/>
+      <c r="F49" s="588"/>
       <c r="G49" s="242" t="s">
         <v>52</v>
       </c>
@@ -41458,15 +41486,15 @@
       </c>
     </row>
     <row r="91" spans="2:14" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B91" s="577" t="s">
+      <c r="B91" s="579" t="s">
         <v>85</v>
       </c>
-      <c r="C91" s="578"/>
+      <c r="C91" s="580"/>
       <c r="D91" s="138"/>
-      <c r="E91" s="579" t="s">
+      <c r="E91" s="587" t="s">
         <v>85</v>
       </c>
-      <c r="F91" s="580"/>
+      <c r="F91" s="588"/>
       <c r="G91" s="242" t="s">
         <v>52</v>
       </c>
@@ -42528,15 +42556,15 @@
       <c r="M129" s="137"/>
     </row>
     <row r="130" spans="2:13" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B130" s="583" t="s">
+      <c r="B130" s="577" t="s">
         <v>86</v>
       </c>
-      <c r="C130" s="584"/>
+      <c r="C130" s="578"/>
       <c r="D130" s="141"/>
-      <c r="E130" s="585" t="s">
+      <c r="E130" s="581" t="s">
         <v>82</v>
       </c>
-      <c r="F130" s="586"/>
+      <c r="F130" s="582"/>
       <c r="G130" s="242" t="s">
         <v>98</v>
       </c>
@@ -42550,8 +42578,8 @@
       <c r="M130" s="576"/>
     </row>
     <row r="131" spans="2:13" ht="21" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E131" s="587"/>
-      <c r="F131" s="588"/>
+      <c r="E131" s="583"/>
+      <c r="F131" s="584"/>
       <c r="G131" s="175"/>
       <c r="H131" s="325"/>
       <c r="I131" s="97"/>
@@ -42569,13 +42597,13 @@
       </c>
     </row>
     <row r="132" spans="2:13" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B132" s="581" t="s">
+      <c r="B132" s="589" t="s">
         <v>82</v>
       </c>
-      <c r="C132" s="582"/>
+      <c r="C132" s="590"/>
       <c r="D132" s="142"/>
-      <c r="E132" s="589"/>
-      <c r="F132" s="590"/>
+      <c r="E132" s="585"/>
+      <c r="F132" s="586"/>
       <c r="G132" s="242" t="s">
         <v>52</v>
       </c>
@@ -43427,15 +43455,15 @@
       <c r="M162" s="137"/>
     </row>
     <row r="163" spans="2:13" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B163" s="583" t="s">
+      <c r="B163" s="577" t="s">
         <v>86</v>
       </c>
-      <c r="C163" s="584"/>
+      <c r="C163" s="578"/>
       <c r="D163" s="141"/>
-      <c r="E163" s="585" t="s">
+      <c r="E163" s="581" t="s">
         <v>82</v>
       </c>
-      <c r="F163" s="586"/>
+      <c r="F163" s="582"/>
       <c r="G163" s="242" t="s">
         <v>98</v>
       </c>
@@ -43449,8 +43477,8 @@
       <c r="M163" s="576"/>
     </row>
     <row r="164" spans="2:13" ht="21" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E164" s="587"/>
-      <c r="F164" s="588"/>
+      <c r="E164" s="583"/>
+      <c r="F164" s="584"/>
       <c r="G164" s="175"/>
       <c r="H164" s="325"/>
       <c r="I164" s="97"/>
@@ -43468,13 +43496,13 @@
       </c>
     </row>
     <row r="165" spans="2:13" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B165" s="581" t="s">
+      <c r="B165" s="589" t="s">
         <v>87</v>
       </c>
-      <c r="C165" s="582"/>
+      <c r="C165" s="590"/>
       <c r="D165" s="142"/>
-      <c r="E165" s="589"/>
-      <c r="F165" s="590"/>
+      <c r="E165" s="585"/>
+      <c r="F165" s="586"/>
       <c r="G165" s="242" t="s">
         <v>52</v>
       </c>
@@ -44326,15 +44354,15 @@
       <c r="M195" s="137"/>
     </row>
     <row r="196" spans="2:13" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B196" s="583" t="s">
+      <c r="B196" s="577" t="s">
         <v>86</v>
       </c>
-      <c r="C196" s="584"/>
+      <c r="C196" s="578"/>
       <c r="D196" s="141"/>
-      <c r="E196" s="585" t="s">
+      <c r="E196" s="581" t="s">
         <v>82</v>
       </c>
-      <c r="F196" s="586"/>
+      <c r="F196" s="582"/>
       <c r="G196" s="242" t="s">
         <v>98</v>
       </c>
@@ -44348,8 +44376,8 @@
       <c r="M196" s="576"/>
     </row>
     <row r="197" spans="2:13" ht="21" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E197" s="587"/>
-      <c r="F197" s="588"/>
+      <c r="E197" s="583"/>
+      <c r="F197" s="584"/>
       <c r="G197" s="175"/>
       <c r="H197" s="325"/>
       <c r="I197" s="97"/>
@@ -44367,13 +44395,13 @@
       </c>
     </row>
     <row r="198" spans="2:13" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B198" s="581" t="s">
+      <c r="B198" s="589" t="s">
         <v>88</v>
       </c>
-      <c r="C198" s="582"/>
+      <c r="C198" s="590"/>
       <c r="D198" s="142"/>
-      <c r="E198" s="589"/>
-      <c r="F198" s="590"/>
+      <c r="E198" s="585"/>
+      <c r="F198" s="586"/>
       <c r="G198" s="242" t="s">
         <v>52</v>
       </c>
@@ -44925,15 +44953,15 @@
       </c>
     </row>
     <row r="219" spans="2:13" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B219" s="577" t="s">
+      <c r="B219" s="579" t="s">
         <v>71</v>
       </c>
-      <c r="C219" s="578"/>
+      <c r="C219" s="580"/>
       <c r="D219" s="138"/>
-      <c r="E219" s="579" t="s">
+      <c r="E219" s="587" t="s">
         <v>82</v>
       </c>
-      <c r="F219" s="580"/>
+      <c r="F219" s="588"/>
       <c r="G219" s="242" t="s">
         <v>52</v>
       </c>
@@ -45431,15 +45459,15 @@
       <c r="F237" s="97"/>
     </row>
     <row r="238" spans="2:13" ht="22.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B238" s="583" t="s">
+      <c r="B238" s="577" t="s">
         <v>89</v>
       </c>
-      <c r="C238" s="584"/>
+      <c r="C238" s="578"/>
       <c r="D238" s="141"/>
-      <c r="E238" s="585" t="s">
+      <c r="E238" s="581" t="s">
         <v>82</v>
       </c>
-      <c r="F238" s="586"/>
+      <c r="F238" s="582"/>
       <c r="G238" s="242" t="s">
         <v>98</v>
       </c>
@@ -45453,8 +45481,8 @@
       <c r="M238" s="576"/>
     </row>
     <row r="239" spans="2:13" ht="22.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E239" s="587"/>
-      <c r="F239" s="588"/>
+      <c r="E239" s="583"/>
+      <c r="F239" s="584"/>
       <c r="G239" s="175"/>
       <c r="H239" s="325"/>
       <c r="I239" s="97"/>
@@ -45472,13 +45500,13 @@
       </c>
     </row>
     <row r="240" spans="2:13" ht="22.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B240" s="581" t="s">
+      <c r="B240" s="589" t="s">
         <v>90</v>
       </c>
-      <c r="C240" s="582"/>
+      <c r="C240" s="590"/>
       <c r="D240" s="142"/>
-      <c r="E240" s="589"/>
-      <c r="F240" s="590"/>
+      <c r="E240" s="585"/>
+      <c r="F240" s="586"/>
       <c r="G240" s="242" t="s">
         <v>52</v>
       </c>
@@ -45802,19 +45830,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="J196:M196"/>
-    <mergeCell ref="J217:M217"/>
-    <mergeCell ref="J238:M238"/>
-    <mergeCell ref="B196:C196"/>
-    <mergeCell ref="B219:C219"/>
-    <mergeCell ref="E196:F198"/>
-    <mergeCell ref="E219:F219"/>
-    <mergeCell ref="B238:C238"/>
-    <mergeCell ref="B240:C240"/>
-    <mergeCell ref="B163:C163"/>
-    <mergeCell ref="B198:C198"/>
-    <mergeCell ref="E238:F240"/>
-    <mergeCell ref="E163:F165"/>
     <mergeCell ref="J4:M4"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="E91:F91"/>
@@ -45830,6 +45845,19 @@
     <mergeCell ref="B130:C130"/>
     <mergeCell ref="B132:C132"/>
     <mergeCell ref="E130:F132"/>
+    <mergeCell ref="B240:C240"/>
+    <mergeCell ref="B163:C163"/>
+    <mergeCell ref="B198:C198"/>
+    <mergeCell ref="E238:F240"/>
+    <mergeCell ref="E163:F165"/>
+    <mergeCell ref="J196:M196"/>
+    <mergeCell ref="J217:M217"/>
+    <mergeCell ref="J238:M238"/>
+    <mergeCell ref="B196:C196"/>
+    <mergeCell ref="B219:C219"/>
+    <mergeCell ref="E196:F198"/>
+    <mergeCell ref="E219:F219"/>
+    <mergeCell ref="B238:C238"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/excel/Glass.xlsx
+++ b/excel/Glass.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ritar/Desktop/SP684-SupplierInfo/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{0E6F1CBA-5FD2-594A-B99B-3F2BFD18ABBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{802F5753-539A-7740-816E-AB4C5684FF31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="600" windowWidth="28800" windowHeight="15860" tabRatio="721" xr2:uid="{769D5609-44B8-DF40-A386-87CBF6C45798}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="721" xr2:uid="{769D5609-44B8-DF40-A386-87CBF6C45798}"/>
   </bookViews>
   <sheets>
     <sheet name="float" sheetId="1" r:id="rId1"/>
@@ -633,16 +633,10 @@
     <t>G01020010106</t>
   </si>
   <si>
-    <t>G01020040505</t>
-  </si>
-  <si>
     <t>G01020030205</t>
   </si>
   <si>
     <t>G01020030206</t>
-  </si>
-  <si>
-    <t>G01020050605</t>
   </si>
   <si>
     <t>G01030010203</t>
@@ -1118,6 +1112,12 @@
   </si>
   <si>
     <t>G01062100106 / G010621401060 / G01062180106</t>
+  </si>
+  <si>
+    <t>G01020050605, G01020040505</t>
+  </si>
+  <si>
+    <t>G01020050606, G01020040506</t>
   </si>
 </sst>
 </file>
@@ -4772,18 +4772,30 @@
     <xf numFmtId="164" fontId="10" fillId="0" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="21" fillId="5" borderId="125" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="5" borderId="126" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="74" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="127" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="5" borderId="76" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="5" borderId="128" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="21" fillId="5" borderId="129" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="21" fillId="5" borderId="130" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="5" borderId="125" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="5" borderId="126" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="5" borderId="123" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4801,18 +4813,6 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="5" borderId="78" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="74" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="127" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="5" borderId="76" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="5" borderId="128" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -5185,7 +5185,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.796875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="12.796875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="27.59765625" style="2" customWidth="1"/>
     <col min="3" max="3" width="14" style="1" customWidth="1"/>
     <col min="4" max="4" width="6.3984375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15" style="9" bestFit="1" customWidth="1"/>
@@ -6211,7 +6211,7 @@
     </row>
     <row r="12" spans="2:54" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="60" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C12" s="21"/>
       <c r="D12" s="257">
@@ -6654,7 +6654,7 @@
     </row>
     <row r="16" spans="2:54" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="60" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C16" s="61"/>
       <c r="D16" s="257">
@@ -9054,7 +9054,7 @@
     </row>
     <row r="38" spans="2:54" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="60" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C38" s="289" t="s">
         <v>2</v>
@@ -9165,7 +9165,7 @@
     </row>
     <row r="39" spans="2:54" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="60" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C39" s="61"/>
       <c r="D39" s="257">
@@ -9274,7 +9274,7 @@
     </row>
     <row r="40" spans="2:54" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="60" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C40" s="61"/>
       <c r="D40" s="257">
@@ -9383,7 +9383,7 @@
     </row>
     <row r="41" spans="2:54" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="60" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C41" s="61"/>
       <c r="D41" s="257">
@@ -9494,7 +9494,7 @@
     </row>
     <row r="42" spans="2:54" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="60" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C42" s="263"/>
       <c r="D42" s="307">
@@ -9707,7 +9707,7 @@
     </row>
     <row r="44" spans="2:54" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="60" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C44" s="61" t="s">
         <v>3</v>
@@ -9818,7 +9818,7 @@
     </row>
     <row r="45" spans="2:54" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="60" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C45" s="61"/>
       <c r="D45" s="257">
@@ -9927,7 +9927,7 @@
     </row>
     <row r="46" spans="2:54" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C46" s="21"/>
       <c r="D46" s="17">
@@ -10035,7 +10035,7 @@
     </row>
     <row r="47" spans="2:54" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C47" s="21"/>
       <c r="D47" s="264">
@@ -10145,7 +10145,7 @@
     </row>
     <row r="48" spans="2:54" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C48" s="21"/>
       <c r="D48" s="257">
@@ -10253,7 +10253,7 @@
     </row>
     <row r="49" spans="2:54" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C49" s="61"/>
       <c r="D49" s="257">
@@ -10362,7 +10362,7 @@
     </row>
     <row r="50" spans="2:54" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C50" s="61"/>
       <c r="D50" s="257">
@@ -10471,7 +10471,7 @@
     </row>
     <row r="51" spans="2:54" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C51" s="287"/>
       <c r="D51" s="257">
@@ -10904,7 +10904,7 @@
     </row>
     <row r="55" spans="2:54" s="504" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="504" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C55" s="478" t="s">
         <v>20</v>
@@ -11015,7 +11015,7 @@
     </row>
     <row r="56" spans="2:54" s="504" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="504" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C56" s="482"/>
       <c r="D56" s="483">
@@ -11562,7 +11562,7 @@
     </row>
     <row r="61" spans="2:54" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="60" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C61" s="289" t="s">
         <v>17</v>
@@ -11673,7 +11673,7 @@
     </row>
     <row r="62" spans="2:54" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="60" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C62" s="263"/>
       <c r="D62" s="291">
@@ -11782,7 +11782,7 @@
     </row>
     <row r="63" spans="2:54" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="60" t="s">
-        <v>199</v>
+        <v>353</v>
       </c>
       <c r="C63" s="289" t="s">
         <v>50</v>
@@ -11893,7 +11893,7 @@
     </row>
     <row r="64" spans="2:54" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="60" t="s">
-        <v>196</v>
+        <v>354</v>
       </c>
       <c r="C64" s="263" t="s">
         <v>51</v>
@@ -12004,7 +12004,7 @@
     </row>
     <row r="65" spans="2:54" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="60" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C65" s="289" t="s">
         <v>119</v>
@@ -12115,7 +12115,7 @@
     </row>
     <row r="66" spans="2:54" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="60" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C66" s="289" t="s">
         <v>4</v>
@@ -12226,7 +12226,7 @@
     </row>
     <row r="67" spans="2:54" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="60" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C67" s="263"/>
       <c r="D67" s="291">
@@ -12335,7 +12335,7 @@
     </row>
     <row r="68" spans="2:54" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="60" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C68" s="61" t="s">
         <v>19</v>
@@ -12446,7 +12446,7 @@
     </row>
     <row r="69" spans="2:54" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="60" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C69" s="287"/>
       <c r="D69" s="257">
@@ -12555,7 +12555,7 @@
     </row>
     <row r="70" spans="2:54" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="60" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C70" s="287"/>
       <c r="D70" s="257">
@@ -12664,7 +12664,7 @@
     </row>
     <row r="71" spans="2:54" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="60" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C71" s="287"/>
       <c r="D71" s="257">
@@ -12773,7 +12773,7 @@
     </row>
     <row r="72" spans="2:54" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="60" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C72" s="298"/>
       <c r="D72" s="291">
@@ -12882,7 +12882,7 @@
     </row>
     <row r="73" spans="2:54" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="60" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C73" s="61" t="s">
         <v>18</v>
@@ -12993,7 +12993,7 @@
     </row>
     <row r="74" spans="2:54" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="60" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C74" s="306"/>
       <c r="D74" s="257">
@@ -13102,7 +13102,7 @@
     </row>
     <row r="75" spans="2:54" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="60" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C75" s="289" t="s">
         <v>21</v>
@@ -13213,7 +13213,7 @@
     </row>
     <row r="76" spans="2:54" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="60" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C76" s="61"/>
       <c r="D76" s="264">
@@ -13322,7 +13322,7 @@
     </row>
     <row r="77" spans="2:54" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="60" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C77" s="61"/>
       <c r="D77" s="257">
@@ -13431,7 +13431,7 @@
     </row>
     <row r="78" spans="2:54" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="60" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C78" s="61"/>
       <c r="D78" s="257">
@@ -13540,7 +13540,7 @@
     </row>
     <row r="79" spans="2:54" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="60" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C79" s="61"/>
       <c r="D79" s="257">
@@ -13649,7 +13649,7 @@
     </row>
     <row r="80" spans="2:54" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="60" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C80" s="21"/>
       <c r="D80" s="22">
@@ -13757,7 +13757,7 @@
     </row>
     <row r="81" spans="2:54" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="60" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C81" s="38"/>
       <c r="D81" s="41">
@@ -13865,7 +13865,7 @@
     </row>
     <row r="82" spans="2:54" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B82" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C82" s="65" t="s">
         <v>32</v>
@@ -14774,7 +14774,7 @@
     </row>
     <row r="95" spans="2:54" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B95" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C95" s="21" t="s">
         <v>1</v>
@@ -14906,7 +14906,7 @@
     </row>
     <row r="96" spans="2:54" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B96" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C96" s="21"/>
       <c r="D96" s="22">
@@ -15036,7 +15036,7 @@
     </row>
     <row r="97" spans="2:51" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B97" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C97" s="21"/>
       <c r="D97" s="22">
@@ -15142,7 +15142,7 @@
     </row>
     <row r="98" spans="2:51" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B98" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C98" s="21"/>
       <c r="D98" s="22">
@@ -15248,7 +15248,7 @@
     </row>
     <row r="99" spans="2:51" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B99" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C99" s="21"/>
       <c r="D99" s="22">
@@ -15356,7 +15356,7 @@
     </row>
     <row r="100" spans="2:51" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B100" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C100" s="21"/>
       <c r="D100" s="22">
@@ -15464,7 +15464,7 @@
     </row>
     <row r="101" spans="2:51" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B101" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C101" s="21"/>
       <c r="D101" s="22">
@@ -15570,7 +15570,7 @@
     </row>
     <row r="102" spans="2:51" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B102" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C102" s="21"/>
       <c r="D102" s="22">
@@ -15676,7 +15676,7 @@
     </row>
     <row r="103" spans="2:51" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B103" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C103" s="21"/>
       <c r="D103" s="22">
@@ -15782,7 +15782,7 @@
     </row>
     <row r="104" spans="2:51" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B104" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C104" s="32"/>
       <c r="D104" s="41">
@@ -15888,7 +15888,7 @@
     </row>
     <row r="105" spans="2:51" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B105" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C105" s="21" t="s">
         <v>3</v>
@@ -15996,7 +15996,7 @@
     </row>
     <row r="106" spans="2:51" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B106" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C106" s="21"/>
       <c r="D106" s="22">
@@ -16102,7 +16102,7 @@
     </row>
     <row r="107" spans="2:51" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B107" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C107" s="21"/>
       <c r="D107" s="17">
@@ -16208,7 +16208,7 @@
     </row>
     <row r="108" spans="2:51" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B108" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C108" s="21"/>
       <c r="D108" s="17">
@@ -16316,7 +16316,7 @@
     </row>
     <row r="109" spans="2:51" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B109" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C109" s="21"/>
       <c r="D109" s="22">
@@ -16422,7 +16422,7 @@
     </row>
     <row r="110" spans="2:51" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B110" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C110" s="21"/>
       <c r="D110" s="22">
@@ -16528,7 +16528,7 @@
     </row>
     <row r="111" spans="2:51" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B111" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C111" s="21"/>
       <c r="D111" s="22">
@@ -16634,7 +16634,7 @@
     </row>
     <row r="112" spans="2:51" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B112" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C112" s="32"/>
       <c r="D112" s="41">
@@ -16740,7 +16740,7 @@
     </row>
     <row r="113" spans="2:54" s="510" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B113" s="60" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C113" s="289" t="s">
         <v>108</v>
@@ -16850,7 +16850,7 @@
     </row>
     <row r="114" spans="2:54" s="510" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B114" s="60" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C114" s="263"/>
       <c r="D114" s="291">
@@ -16958,7 +16958,7 @@
     </row>
     <row r="115" spans="2:54" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B115" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C115" s="34" t="s">
         <v>5</v>
@@ -17066,7 +17066,7 @@
     </row>
     <row r="116" spans="2:54" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B116" s="60" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C116" s="61"/>
       <c r="D116" s="257">
@@ -17174,7 +17174,7 @@
     </row>
     <row r="117" spans="2:54" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B117" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C117" s="21"/>
       <c r="D117" s="22">
@@ -17280,7 +17280,7 @@
     </row>
     <row r="118" spans="2:54" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B118" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C118" s="21"/>
       <c r="D118" s="22">
@@ -17386,7 +17386,7 @@
     </row>
     <row r="119" spans="2:54" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B119" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C119" s="32"/>
       <c r="D119" s="41">
@@ -17703,7 +17703,7 @@
     </row>
     <row r="122" spans="2:54" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B122" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C122" s="34" t="s">
         <v>119</v>
@@ -17811,7 +17811,7 @@
     </row>
     <row r="123" spans="2:54" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B123" s="60" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C123" s="263"/>
       <c r="D123" s="307">
@@ -17920,7 +17920,7 @@
     </row>
     <row r="124" spans="2:54" s="69" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B124" s="69" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C124" s="70" t="s">
         <v>21</v>
@@ -18030,7 +18030,7 @@
     </row>
     <row r="125" spans="2:54" s="69" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B125" s="69" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C125" s="76"/>
       <c r="D125" s="77">
@@ -18138,7 +18138,7 @@
     </row>
     <row r="126" spans="2:54" s="69" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B126" s="69" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C126" s="76"/>
       <c r="D126" s="77">
@@ -18246,7 +18246,7 @@
     </row>
     <row r="127" spans="2:54" s="69" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B127" s="69" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C127" s="76"/>
       <c r="D127" s="77">
@@ -18354,7 +18354,7 @@
     </row>
     <row r="128" spans="2:54" s="69" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B128" s="69" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C128" s="76"/>
       <c r="D128" s="77">
@@ -18462,7 +18462,7 @@
     </row>
     <row r="129" spans="2:53" s="69" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B129" s="69" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C129" s="90"/>
       <c r="D129" s="80">
@@ -19970,7 +19970,7 @@
     </row>
     <row r="153" spans="2:53" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B153" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C153" s="21" t="s">
         <v>1</v>
@@ -20060,7 +20060,7 @@
     </row>
     <row r="154" spans="2:53" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B154" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C154" s="61"/>
       <c r="D154" s="257">
@@ -20150,7 +20150,7 @@
     </row>
     <row r="155" spans="2:53" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B155" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C155" s="61"/>
       <c r="D155" s="257">
@@ -20242,7 +20242,7 @@
     </row>
     <row r="156" spans="2:53" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B156" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C156" s="61"/>
       <c r="D156" s="257">
@@ -20332,7 +20332,7 @@
     </row>
     <row r="157" spans="2:53" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B157" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C157" s="61"/>
       <c r="D157" s="257">
@@ -20422,7 +20422,7 @@
     </row>
     <row r="158" spans="2:53" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B158" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C158" s="263"/>
       <c r="D158" s="291">
@@ -20512,7 +20512,7 @@
     </row>
     <row r="159" spans="2:53" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B159" s="60" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C159" s="61" t="s">
         <v>2</v>
@@ -20606,7 +20606,7 @@
     </row>
     <row r="160" spans="2:53" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B160" s="60" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C160" s="263"/>
       <c r="D160" s="307">
@@ -20698,7 +20698,7 @@
     </row>
     <row r="161" spans="2:53" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B161" s="60" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C161" s="61" t="s">
         <v>3</v>
@@ -20790,7 +20790,7 @@
     </row>
     <row r="162" spans="2:53" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B162" s="60" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C162" s="61"/>
       <c r="D162" s="257">
@@ -20882,7 +20882,7 @@
     </row>
     <row r="163" spans="2:53" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B163" s="60" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C163" s="61"/>
       <c r="D163" s="264">
@@ -20974,7 +20974,7 @@
     </row>
     <row r="164" spans="2:53" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B164" s="60" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C164" s="61"/>
       <c r="D164" s="257">
@@ -21064,7 +21064,7 @@
     </row>
     <row r="165" spans="2:53" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B165" s="60" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C165" s="263"/>
       <c r="D165" s="291">
@@ -21330,7 +21330,7 @@
     </row>
     <row r="168" spans="2:53" s="60" customFormat="1" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B168" s="60" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C168" s="289" t="s">
         <v>157</v>
@@ -21398,7 +21398,7 @@
     </row>
     <row r="169" spans="2:53" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B169" s="60" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C169" s="61"/>
       <c r="D169" s="450">
@@ -21464,7 +21464,7 @@
     </row>
     <row r="170" spans="2:53" s="60" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B170" s="60" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C170" s="536"/>
       <c r="D170" s="274">
@@ -22768,7 +22768,7 @@
     </row>
     <row r="191" spans="2:64" s="60" customFormat="1" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B191" s="60" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C191" s="61" t="s">
         <v>15</v>
@@ -22935,7 +22935,7 @@
     </row>
     <row r="192" spans="2:64" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B192" s="60" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C192" s="61"/>
       <c r="D192" s="264">
@@ -23100,7 +23100,7 @@
     </row>
     <row r="193" spans="2:64" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B193" s="60" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C193" s="61"/>
       <c r="D193" s="257">
@@ -23265,7 +23265,7 @@
     </row>
     <row r="194" spans="2:64" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B194" s="60" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C194" s="287"/>
       <c r="D194" s="257">
@@ -23410,7 +23410,7 @@
     </row>
     <row r="195" spans="2:64" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B195" s="60" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C195" s="287"/>
       <c r="D195" s="257">
@@ -23557,7 +23557,7 @@
     </row>
     <row r="196" spans="2:64" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B196" s="60" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C196" s="287"/>
       <c r="D196" s="299">
@@ -23700,7 +23700,7 @@
     </row>
     <row r="197" spans="2:64" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B197" s="60" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C197" s="287"/>
       <c r="D197" s="450">
@@ -23983,7 +23983,7 @@
     </row>
     <row r="199" spans="2:64" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B199" s="60" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C199" s="272" t="s">
         <v>142</v>
@@ -24099,7 +24099,7 @@
     </row>
     <row r="200" spans="2:64" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B200" s="60" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C200" s="61"/>
       <c r="D200" s="450">
@@ -24213,7 +24213,7 @@
     </row>
     <row r="201" spans="2:64" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B201" s="60" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C201" s="263"/>
       <c r="D201" s="291">
@@ -24327,7 +24327,7 @@
     </row>
     <row r="202" spans="2:64" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B202" s="60" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C202" s="289" t="s">
         <v>16</v>
@@ -24552,7 +24552,7 @@
     </row>
     <row r="204" spans="2:64" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B204" s="60" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C204" s="61" t="s">
         <v>95</v>
@@ -24666,7 +24666,7 @@
     </row>
     <row r="205" spans="2:64" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B205" s="60" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C205" s="61"/>
       <c r="D205" s="299">
@@ -24778,7 +24778,7 @@
     </row>
     <row r="206" spans="2:64" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B206" s="60" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C206" s="62" t="s">
         <v>143</v>
@@ -24894,7 +24894,7 @@
     </row>
     <row r="207" spans="2:64" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B207" s="60" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C207" s="289" t="s">
         <v>16</v>
@@ -25337,7 +25337,7 @@
     </row>
     <row r="211" spans="2:57" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B211" s="60" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C211" s="62" t="s">
         <v>144</v>
@@ -25453,7 +25453,7 @@
     </row>
     <row r="212" spans="2:57" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B212" s="60" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C212" s="289" t="s">
         <v>150</v>
@@ -25569,7 +25569,7 @@
     </row>
     <row r="213" spans="2:57" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B213" s="60" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C213" s="61" t="s">
         <v>151</v>
@@ -25685,7 +25685,7 @@
     </row>
     <row r="214" spans="2:57" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B214" s="60" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C214" s="287" t="s">
         <v>152</v>
@@ -29262,7 +29262,7 @@
     </row>
     <row r="253" spans="2:53" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B253" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C253" s="21" t="s">
         <v>1</v>
@@ -29370,7 +29370,7 @@
     </row>
     <row r="254" spans="2:53" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B254" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C254" s="21"/>
       <c r="D254" s="22">
@@ -29476,7 +29476,7 @@
     </row>
     <row r="255" spans="2:53" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B255" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C255" s="21"/>
       <c r="D255" s="22">
@@ -29585,7 +29585,7 @@
     </row>
     <row r="256" spans="2:53" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B256" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C256" s="21"/>
       <c r="D256" s="22">
@@ -30003,7 +30003,7 @@
     </row>
     <row r="260" spans="2:53" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B260" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C260" s="38"/>
       <c r="D260" s="41">
@@ -30317,7 +30317,7 @@
     </row>
     <row r="263" spans="2:53" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B263" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C263" s="21"/>
       <c r="D263" s="22">
@@ -30529,7 +30529,7 @@
     </row>
     <row r="265" spans="2:53" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B265" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C265" s="407" t="s">
         <v>3</v>
@@ -30640,7 +30640,7 @@
     </row>
     <row r="266" spans="2:53" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B266" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C266" s="52" t="s">
         <v>102</v>
@@ -30748,7 +30748,7 @@
     </row>
     <row r="267" spans="2:53" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B267" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C267" s="21" t="s">
         <v>5</v>
@@ -30856,7 +30856,7 @@
     </row>
     <row r="268" spans="2:53" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B268" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C268" s="21"/>
       <c r="D268" s="22">
@@ -30962,7 +30962,7 @@
     </row>
     <row r="269" spans="2:53" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B269" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C269" s="38"/>
       <c r="D269" s="41">
@@ -31068,7 +31068,7 @@
     </row>
     <row r="270" spans="2:53" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B270" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C270" s="21" t="s">
         <v>15</v>
@@ -31178,7 +31178,7 @@
     </row>
     <row r="271" spans="2:53" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B271" s="60" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C271" s="61"/>
       <c r="D271" s="257">
@@ -31288,7 +31288,7 @@
     </row>
     <row r="272" spans="2:53" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B272" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C272" s="21"/>
       <c r="D272" s="22">
@@ -31396,7 +31396,7 @@
     </row>
     <row r="273" spans="2:51" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B273" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C273" s="21"/>
       <c r="D273" s="22">
@@ -31504,7 +31504,7 @@
     </row>
     <row r="274" spans="2:51" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B274" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C274" s="21"/>
       <c r="D274" s="22">
@@ -31612,7 +31612,7 @@
     </row>
     <row r="275" spans="2:51" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B275" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C275" s="52" t="s">
         <v>16</v>
@@ -31722,7 +31722,7 @@
     </row>
     <row r="276" spans="2:51" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B276" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C276" s="52" t="s">
         <v>32</v>
@@ -31831,7 +31831,7 @@
     </row>
     <row r="277" spans="2:51" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B277" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C277" s="52" t="s">
         <v>31</v>
@@ -31939,7 +31939,7 @@
     </row>
     <row r="278" spans="2:51" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B278" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C278" s="34" t="s">
         <v>21</v>
@@ -32047,7 +32047,7 @@
     </row>
     <row r="279" spans="2:51" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B279" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C279" s="21"/>
       <c r="D279" s="22">
@@ -32153,7 +32153,7 @@
     </row>
     <row r="280" spans="2:51" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B280" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C280" s="21"/>
       <c r="D280" s="22">
@@ -32259,7 +32259,7 @@
     </row>
     <row r="281" spans="2:51" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B281" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C281" s="21"/>
       <c r="D281" s="22">
@@ -32365,7 +32365,7 @@
     </row>
     <row r="282" spans="2:51" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B282" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C282" s="21"/>
       <c r="D282" s="22">
@@ -32471,7 +32471,7 @@
     </row>
     <row r="283" spans="2:51" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B283" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C283" s="31"/>
       <c r="D283" s="22">
@@ -32577,7 +32577,7 @@
     </row>
     <row r="284" spans="2:51" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B284" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C284" s="38"/>
       <c r="D284" s="41">
@@ -32683,7 +32683,7 @@
     </row>
     <row r="285" spans="2:51" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B285" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C285" s="34" t="s">
         <v>36</v>
@@ -32791,7 +32791,7 @@
     </row>
     <row r="286" spans="2:51" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B286" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C286" s="21"/>
       <c r="D286" s="22">
@@ -32897,7 +32897,7 @@
     </row>
     <row r="287" spans="2:51" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B287" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C287" s="31"/>
       <c r="D287" s="22">
@@ -33003,7 +33003,7 @@
     </row>
     <row r="288" spans="2:51" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B288" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C288" s="38"/>
       <c r="D288" s="41">
@@ -33214,7 +33214,7 @@
     </row>
     <row r="290" spans="2:53" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B290" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C290" s="38"/>
       <c r="D290" s="41">
@@ -33320,7 +33320,7 @@
     </row>
     <row r="291" spans="2:53" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B291" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C291" s="34" t="s">
         <v>38</v>
@@ -33428,7 +33428,7 @@
     </row>
     <row r="292" spans="2:53" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B292" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C292" s="38" t="s">
         <v>39</v>
@@ -33959,7 +33959,7 @@
     </row>
     <row r="7" spans="2:36" s="60" customFormat="1" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B7" s="60" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C7" s="272" t="s">
         <v>57</v>
@@ -34042,7 +34042,7 @@
     </row>
     <row r="8" spans="2:36" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="60" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C8" s="61" t="s">
         <v>60</v>
@@ -34117,7 +34117,7 @@
     </row>
     <row r="9" spans="2:36" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="60" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C9" s="61"/>
       <c r="D9" s="257">
@@ -34330,7 +34330,7 @@
     </row>
     <row r="12" spans="2:36" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="60" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C12" s="272" t="s">
         <v>63</v>
@@ -34405,7 +34405,7 @@
     </row>
     <row r="13" spans="2:36" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="60" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C13" s="61" t="s">
         <v>61</v>
@@ -34480,7 +34480,7 @@
     </row>
     <row r="14" spans="2:36" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="60" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C14" s="263" t="s">
         <v>148</v>
@@ -34555,7 +34555,7 @@
     </row>
     <row r="15" spans="2:36" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="60" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C15" s="272" t="s">
         <v>62</v>
@@ -34630,7 +34630,7 @@
     </row>
     <row r="16" spans="2:36" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="60" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C16" s="61" t="s">
         <v>64</v>
@@ -34705,7 +34705,7 @@
     </row>
     <row r="17" spans="2:36" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="60" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C17" s="272" t="s">
         <v>65</v>
@@ -34780,7 +34780,7 @@
     </row>
     <row r="18" spans="2:36" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="60" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C18" s="61" t="s">
         <v>149</v>
@@ -34863,7 +34863,7 @@
     </row>
     <row r="19" spans="2:36" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="60" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C19" s="61"/>
       <c r="D19" s="291">
@@ -34936,7 +34936,7 @@
     </row>
     <row r="20" spans="2:36" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="60" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C20" s="272" t="s">
         <v>57</v>
@@ -35011,7 +35011,7 @@
     </row>
     <row r="21" spans="2:36" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="60" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C21" s="61" t="s">
         <v>66</v>
@@ -35086,7 +35086,7 @@
     </row>
     <row r="22" spans="2:36" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="60" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C22" s="61"/>
       <c r="D22" s="257">
@@ -35159,7 +35159,7 @@
     </row>
     <row r="23" spans="2:36" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="60" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C23" s="61"/>
       <c r="D23" s="257">
@@ -35232,7 +35232,7 @@
     </row>
     <row r="24" spans="2:36" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="60" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C24" s="263"/>
       <c r="D24" s="291">
@@ -35305,7 +35305,7 @@
     </row>
     <row r="25" spans="2:36" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="60" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C25" s="61" t="s">
         <v>57</v>
@@ -35380,7 +35380,7 @@
     </row>
     <row r="26" spans="2:36" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="60" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C26" s="263" t="s">
         <v>67</v>
@@ -35455,7 +35455,7 @@
     </row>
     <row r="27" spans="2:36" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="60" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C27" s="272" t="s">
         <v>104</v>
@@ -35530,7 +35530,7 @@
     </row>
     <row r="28" spans="2:36" s="60" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="60" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C28" s="61"/>
       <c r="D28" s="257">
@@ -35603,7 +35603,7 @@
     </row>
     <row r="29" spans="2:36" s="60" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B29" s="60" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C29" s="263"/>
       <c r="D29" s="291">
@@ -39208,15 +39208,15 @@
       </c>
     </row>
     <row r="6" spans="2:14" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="579" t="s">
+      <c r="B6" s="577" t="s">
         <v>82</v>
       </c>
-      <c r="C6" s="580"/>
+      <c r="C6" s="578"/>
       <c r="D6" s="114"/>
-      <c r="E6" s="587" t="s">
+      <c r="E6" s="579" t="s">
         <v>82</v>
       </c>
-      <c r="F6" s="588"/>
+      <c r="F6" s="580"/>
       <c r="G6" s="242" t="s">
         <v>52</v>
       </c>
@@ -40362,15 +40362,15 @@
       </c>
     </row>
     <row r="49" spans="2:13" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="579" t="s">
+      <c r="B49" s="577" t="s">
         <v>85</v>
       </c>
-      <c r="C49" s="580"/>
+      <c r="C49" s="578"/>
       <c r="D49" s="138"/>
-      <c r="E49" s="587" t="s">
+      <c r="E49" s="579" t="s">
         <v>82</v>
       </c>
-      <c r="F49" s="588"/>
+      <c r="F49" s="580"/>
       <c r="G49" s="242" t="s">
         <v>52</v>
       </c>
@@ -41486,15 +41486,15 @@
       </c>
     </row>
     <row r="91" spans="2:14" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B91" s="579" t="s">
+      <c r="B91" s="577" t="s">
         <v>85</v>
       </c>
-      <c r="C91" s="580"/>
+      <c r="C91" s="578"/>
       <c r="D91" s="138"/>
-      <c r="E91" s="587" t="s">
+      <c r="E91" s="579" t="s">
         <v>85</v>
       </c>
-      <c r="F91" s="588"/>
+      <c r="F91" s="580"/>
       <c r="G91" s="242" t="s">
         <v>52</v>
       </c>
@@ -42556,15 +42556,15 @@
       <c r="M129" s="137"/>
     </row>
     <row r="130" spans="2:13" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B130" s="577" t="s">
+      <c r="B130" s="583" t="s">
         <v>86</v>
       </c>
-      <c r="C130" s="578"/>
+      <c r="C130" s="584"/>
       <c r="D130" s="141"/>
-      <c r="E130" s="581" t="s">
+      <c r="E130" s="585" t="s">
         <v>82</v>
       </c>
-      <c r="F130" s="582"/>
+      <c r="F130" s="586"/>
       <c r="G130" s="242" t="s">
         <v>98</v>
       </c>
@@ -42578,8 +42578,8 @@
       <c r="M130" s="576"/>
     </row>
     <row r="131" spans="2:13" ht="21" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E131" s="583"/>
-      <c r="F131" s="584"/>
+      <c r="E131" s="587"/>
+      <c r="F131" s="588"/>
       <c r="G131" s="175"/>
       <c r="H131" s="325"/>
       <c r="I131" s="97"/>
@@ -42597,13 +42597,13 @@
       </c>
     </row>
     <row r="132" spans="2:13" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B132" s="589" t="s">
+      <c r="B132" s="581" t="s">
         <v>82</v>
       </c>
-      <c r="C132" s="590"/>
+      <c r="C132" s="582"/>
       <c r="D132" s="142"/>
-      <c r="E132" s="585"/>
-      <c r="F132" s="586"/>
+      <c r="E132" s="589"/>
+      <c r="F132" s="590"/>
       <c r="G132" s="242" t="s">
         <v>52</v>
       </c>
@@ -43455,15 +43455,15 @@
       <c r="M162" s="137"/>
     </row>
     <row r="163" spans="2:13" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B163" s="577" t="s">
+      <c r="B163" s="583" t="s">
         <v>86</v>
       </c>
-      <c r="C163" s="578"/>
+      <c r="C163" s="584"/>
       <c r="D163" s="141"/>
-      <c r="E163" s="581" t="s">
+      <c r="E163" s="585" t="s">
         <v>82</v>
       </c>
-      <c r="F163" s="582"/>
+      <c r="F163" s="586"/>
       <c r="G163" s="242" t="s">
         <v>98</v>
       </c>
@@ -43477,8 +43477,8 @@
       <c r="M163" s="576"/>
     </row>
     <row r="164" spans="2:13" ht="21" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E164" s="583"/>
-      <c r="F164" s="584"/>
+      <c r="E164" s="587"/>
+      <c r="F164" s="588"/>
       <c r="G164" s="175"/>
       <c r="H164" s="325"/>
       <c r="I164" s="97"/>
@@ -43496,13 +43496,13 @@
       </c>
     </row>
     <row r="165" spans="2:13" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B165" s="589" t="s">
+      <c r="B165" s="581" t="s">
         <v>87</v>
       </c>
-      <c r="C165" s="590"/>
+      <c r="C165" s="582"/>
       <c r="D165" s="142"/>
-      <c r="E165" s="585"/>
-      <c r="F165" s="586"/>
+      <c r="E165" s="589"/>
+      <c r="F165" s="590"/>
       <c r="G165" s="242" t="s">
         <v>52</v>
       </c>
@@ -44354,15 +44354,15 @@
       <c r="M195" s="137"/>
     </row>
     <row r="196" spans="2:13" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B196" s="577" t="s">
+      <c r="B196" s="583" t="s">
         <v>86</v>
       </c>
-      <c r="C196" s="578"/>
+      <c r="C196" s="584"/>
       <c r="D196" s="141"/>
-      <c r="E196" s="581" t="s">
+      <c r="E196" s="585" t="s">
         <v>82</v>
       </c>
-      <c r="F196" s="582"/>
+      <c r="F196" s="586"/>
       <c r="G196" s="242" t="s">
         <v>98</v>
       </c>
@@ -44376,8 +44376,8 @@
       <c r="M196" s="576"/>
     </row>
     <row r="197" spans="2:13" ht="21" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E197" s="583"/>
-      <c r="F197" s="584"/>
+      <c r="E197" s="587"/>
+      <c r="F197" s="588"/>
       <c r="G197" s="175"/>
       <c r="H197" s="325"/>
       <c r="I197" s="97"/>
@@ -44395,13 +44395,13 @@
       </c>
     </row>
     <row r="198" spans="2:13" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B198" s="589" t="s">
+      <c r="B198" s="581" t="s">
         <v>88</v>
       </c>
-      <c r="C198" s="590"/>
+      <c r="C198" s="582"/>
       <c r="D198" s="142"/>
-      <c r="E198" s="585"/>
-      <c r="F198" s="586"/>
+      <c r="E198" s="589"/>
+      <c r="F198" s="590"/>
       <c r="G198" s="242" t="s">
         <v>52</v>
       </c>
@@ -44953,15 +44953,15 @@
       </c>
     </row>
     <row r="219" spans="2:13" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B219" s="579" t="s">
+      <c r="B219" s="577" t="s">
         <v>71</v>
       </c>
-      <c r="C219" s="580"/>
+      <c r="C219" s="578"/>
       <c r="D219" s="138"/>
-      <c r="E219" s="587" t="s">
+      <c r="E219" s="579" t="s">
         <v>82</v>
       </c>
-      <c r="F219" s="588"/>
+      <c r="F219" s="580"/>
       <c r="G219" s="242" t="s">
         <v>52</v>
       </c>
@@ -45459,15 +45459,15 @@
       <c r="F237" s="97"/>
     </row>
     <row r="238" spans="2:13" ht="22.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B238" s="577" t="s">
+      <c r="B238" s="583" t="s">
         <v>89</v>
       </c>
-      <c r="C238" s="578"/>
+      <c r="C238" s="584"/>
       <c r="D238" s="141"/>
-      <c r="E238" s="581" t="s">
+      <c r="E238" s="585" t="s">
         <v>82</v>
       </c>
-      <c r="F238" s="582"/>
+      <c r="F238" s="586"/>
       <c r="G238" s="242" t="s">
         <v>98</v>
       </c>
@@ -45481,8 +45481,8 @@
       <c r="M238" s="576"/>
     </row>
     <row r="239" spans="2:13" ht="22.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E239" s="583"/>
-      <c r="F239" s="584"/>
+      <c r="E239" s="587"/>
+      <c r="F239" s="588"/>
       <c r="G239" s="175"/>
       <c r="H239" s="325"/>
       <c r="I239" s="97"/>
@@ -45500,13 +45500,13 @@
       </c>
     </row>
     <row r="240" spans="2:13" ht="22.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B240" s="589" t="s">
+      <c r="B240" s="581" t="s">
         <v>90</v>
       </c>
-      <c r="C240" s="590"/>
+      <c r="C240" s="582"/>
       <c r="D240" s="142"/>
-      <c r="E240" s="585"/>
-      <c r="F240" s="586"/>
+      <c r="E240" s="589"/>
+      <c r="F240" s="590"/>
       <c r="G240" s="242" t="s">
         <v>52</v>
       </c>
@@ -45830,6 +45830,19 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="J196:M196"/>
+    <mergeCell ref="J217:M217"/>
+    <mergeCell ref="J238:M238"/>
+    <mergeCell ref="B196:C196"/>
+    <mergeCell ref="B219:C219"/>
+    <mergeCell ref="E196:F198"/>
+    <mergeCell ref="E219:F219"/>
+    <mergeCell ref="B238:C238"/>
+    <mergeCell ref="B240:C240"/>
+    <mergeCell ref="B163:C163"/>
+    <mergeCell ref="B198:C198"/>
+    <mergeCell ref="E238:F240"/>
+    <mergeCell ref="E163:F165"/>
     <mergeCell ref="J4:M4"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="E91:F91"/>
@@ -45845,19 +45858,6 @@
     <mergeCell ref="B130:C130"/>
     <mergeCell ref="B132:C132"/>
     <mergeCell ref="E130:F132"/>
-    <mergeCell ref="B240:C240"/>
-    <mergeCell ref="B163:C163"/>
-    <mergeCell ref="B198:C198"/>
-    <mergeCell ref="E238:F240"/>
-    <mergeCell ref="E163:F165"/>
-    <mergeCell ref="J196:M196"/>
-    <mergeCell ref="J217:M217"/>
-    <mergeCell ref="J238:M238"/>
-    <mergeCell ref="B196:C196"/>
-    <mergeCell ref="B219:C219"/>
-    <mergeCell ref="E196:F198"/>
-    <mergeCell ref="E219:F219"/>
-    <mergeCell ref="B238:C238"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait"/>
